--- a/uploads/invoice-fee.xlsx
+++ b/uploads/invoice-fee.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\coralis\20251021\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\coralis\20251031\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C191F800-6135-496F-B256-A648C4D41203}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51FEDFE2-5E77-48D5-AA26-CB75D48550B4}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sales Outstanding Fee" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="21">
   <si>
     <t>nomor_invoice</t>
   </si>
@@ -37,31 +37,13 @@
     <t>ex: angka</t>
   </si>
   <si>
-    <t>17BSB25000131</t>
+    <t>17BSB25000146</t>
   </si>
   <si>
     <t>Ongkos Kirim</t>
   </si>
   <si>
-    <t>17BSB25000139</t>
-  </si>
-  <si>
-    <t>17BSB25000140</t>
-  </si>
-  <si>
-    <t>17BSB25000141</t>
-  </si>
-  <si>
-    <t>17BSB25000142</t>
-  </si>
-  <si>
-    <t>17BSB25000146</t>
-  </si>
-  <si>
     <t>17BSB25000171</t>
-  </si>
-  <si>
-    <t>17BSB25000178</t>
   </si>
   <si>
     <t>17BSB25000268</t>
@@ -375,10 +357,10 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:Z24"/>
-  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:Z18"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -389,7 +371,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -423,7 +405,7 @@
       <c r="Y2" s="3"/>
       <c r="Z2" s="3"/>
     </row>
-    <row r="4" spans="1:26" s="4" customFormat="1" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:26" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>5</v>
       </c>
@@ -431,10 +413,10 @@
         <v>6</v>
       </c>
       <c r="C4" s="4">
-        <v>170455</v>
-      </c>
-    </row>
-    <row r="5" spans="1:26" s="4" customFormat="1" ht="12.5" x14ac:dyDescent="0.25">
+        <v>2343000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
         <v>7</v>
       </c>
@@ -442,10 +424,10 @@
         <v>6</v>
       </c>
       <c r="C5" s="4">
-        <v>4510000</v>
-      </c>
-    </row>
-    <row r="6" spans="1:26" s="4" customFormat="1" ht="12.5" x14ac:dyDescent="0.25">
+        <v>912070</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
         <v>8</v>
       </c>
@@ -453,10 +435,10 @@
         <v>6</v>
       </c>
       <c r="C6" s="4">
-        <v>4510000</v>
-      </c>
-    </row>
-    <row r="7" spans="1:26" s="4" customFormat="1" ht="12.5" x14ac:dyDescent="0.25">
+        <v>1009031</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
         <v>9</v>
       </c>
@@ -464,10 +446,10 @@
         <v>6</v>
       </c>
       <c r="C7" s="4">
-        <v>4587500</v>
-      </c>
-    </row>
-    <row r="8" spans="1:26" s="4" customFormat="1" ht="12.5" x14ac:dyDescent="0.25">
+        <v>1519940</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
         <v>10</v>
       </c>
@@ -475,10 +457,10 @@
         <v>6</v>
       </c>
       <c r="C8" s="4">
-        <v>4587500</v>
-      </c>
-    </row>
-    <row r="9" spans="1:26" s="4" customFormat="1" ht="12.5" x14ac:dyDescent="0.25">
+        <v>3467820</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
         <v>11</v>
       </c>
@@ -486,10 +468,10 @@
         <v>6</v>
       </c>
       <c r="C9" s="4">
-        <v>2343000</v>
-      </c>
-    </row>
-    <row r="10" spans="1:26" s="4" customFormat="1" ht="12.5" x14ac:dyDescent="0.25">
+        <v>878130</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
         <v>12</v>
       </c>
@@ -497,10 +479,10 @@
         <v>6</v>
       </c>
       <c r="C10" s="4">
-        <v>912070</v>
-      </c>
-    </row>
-    <row r="11" spans="1:26" s="4" customFormat="1" ht="12.5" x14ac:dyDescent="0.25">
+        <v>857640</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
         <v>13</v>
       </c>
@@ -508,10 +490,10 @@
         <v>6</v>
       </c>
       <c r="C11" s="4">
-        <v>325089</v>
-      </c>
-    </row>
-    <row r="12" spans="1:26" s="4" customFormat="1" ht="12.5" x14ac:dyDescent="0.25">
+        <v>2716080</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
         <v>14</v>
       </c>
@@ -519,10 +501,10 @@
         <v>6</v>
       </c>
       <c r="C12" s="4">
-        <v>1009031</v>
-      </c>
-    </row>
-    <row r="13" spans="1:26" s="4" customFormat="1" ht="12.5" x14ac:dyDescent="0.25">
+        <v>1381240</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
         <v>15</v>
       </c>
@@ -530,10 +512,10 @@
         <v>6</v>
       </c>
       <c r="C13" s="4">
-        <v>1519940</v>
-      </c>
-    </row>
-    <row r="14" spans="1:26" s="4" customFormat="1" ht="12.5" x14ac:dyDescent="0.25">
+        <v>4718730</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
         <v>16</v>
       </c>
@@ -541,10 +523,10 @@
         <v>6</v>
       </c>
       <c r="C14" s="4">
-        <v>3467820</v>
-      </c>
-    </row>
-    <row r="15" spans="1:26" s="4" customFormat="1" ht="12.5" x14ac:dyDescent="0.25">
+        <v>2200410</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
         <v>17</v>
       </c>
@@ -552,10 +534,10 @@
         <v>6</v>
       </c>
       <c r="C15" s="4">
-        <v>878130</v>
-      </c>
-    </row>
-    <row r="16" spans="1:26" s="4" customFormat="1" ht="12.5" x14ac:dyDescent="0.25">
+        <v>73320</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
         <v>18</v>
       </c>
@@ -563,10 +545,10 @@
         <v>6</v>
       </c>
       <c r="C16" s="4">
-        <v>857640</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" s="4" customFormat="1" ht="12.5" x14ac:dyDescent="0.25">
+        <v>419420</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
         <v>19</v>
       </c>
@@ -574,10 +556,10 @@
         <v>6</v>
       </c>
       <c r="C17" s="4">
-        <v>2716080</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" s="4" customFormat="1" ht="12.5" x14ac:dyDescent="0.25">
+        <v>2044780</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
         <v>20</v>
       </c>
@@ -585,72 +567,6 @@
         <v>6</v>
       </c>
       <c r="C18" s="4">
-        <v>1381240</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" s="4" customFormat="1" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C19" s="4">
-        <v>4718730</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" s="4" customFormat="1" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C20" s="4">
-        <v>2200410</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" s="4" customFormat="1" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C21" s="4">
-        <v>73320</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" s="4" customFormat="1" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A22" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C22" s="4">
-        <v>419420</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" s="4" customFormat="1" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A23" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C23" s="4">
-        <v>2044780</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" s="4" customFormat="1" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C24" s="4">
         <v>340920</v>
       </c>
     </row>

--- a/uploads/invoice-fee.xlsx
+++ b/uploads/invoice-fee.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\coralis\20251031\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Coralis\Eksport Implementasi\20251114\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51FEDFE2-5E77-48D5-AA26-CB75D48550B4}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12585"/>
   </bookViews>
   <sheets>
     <sheet name="Sales Outstanding Fee" sheetId="1" r:id="rId1"/>
@@ -20,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="24">
   <si>
     <t>nomor_invoice</t>
   </si>
@@ -37,10 +36,19 @@
     <t>ex: angka</t>
   </si>
   <si>
+    <t>14BSB25003328</t>
+  </si>
+  <si>
+    <t>Ongkos Kirim</t>
+  </si>
+  <si>
+    <t>02BSB24000550</t>
+  </si>
+  <si>
+    <t>05ASB25012983</t>
+  </si>
+  <si>
     <t>17BSB25000146</t>
-  </si>
-  <si>
-    <t>Ongkos Kirim</t>
   </si>
   <si>
     <t>17BSB25000171</t>
@@ -88,7 +96,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -353,11 +361,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:Z18"/>
+  <dimension ref="A1:Z21"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:26" x14ac:dyDescent="0.2">
@@ -413,7 +421,7 @@
         <v>6</v>
       </c>
       <c r="C4" s="4">
-        <v>2343000</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:26" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
@@ -424,7 +432,7 @@
         <v>6</v>
       </c>
       <c r="C5" s="4">
-        <v>912070</v>
+        <v>1171171</v>
       </c>
     </row>
     <row r="6" spans="1:26" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
@@ -435,7 +443,7 @@
         <v>6</v>
       </c>
       <c r="C6" s="4">
-        <v>1009031</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:26" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
@@ -446,7 +454,7 @@
         <v>6</v>
       </c>
       <c r="C7" s="4">
-        <v>1519940</v>
+        <v>2343000</v>
       </c>
     </row>
     <row r="8" spans="1:26" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
@@ -457,7 +465,7 @@
         <v>6</v>
       </c>
       <c r="C8" s="4">
-        <v>3467820</v>
+        <v>912070</v>
       </c>
     </row>
     <row r="9" spans="1:26" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
@@ -468,7 +476,7 @@
         <v>6</v>
       </c>
       <c r="C9" s="4">
-        <v>878130</v>
+        <v>1009031</v>
       </c>
     </row>
     <row r="10" spans="1:26" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
@@ -479,7 +487,7 @@
         <v>6</v>
       </c>
       <c r="C10" s="4">
-        <v>857640</v>
+        <v>1519940</v>
       </c>
     </row>
     <row r="11" spans="1:26" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
@@ -490,7 +498,7 @@
         <v>6</v>
       </c>
       <c r="C11" s="4">
-        <v>2716080</v>
+        <v>3467820</v>
       </c>
     </row>
     <row r="12" spans="1:26" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
@@ -501,7 +509,7 @@
         <v>6</v>
       </c>
       <c r="C12" s="4">
-        <v>1381240</v>
+        <v>878130</v>
       </c>
     </row>
     <row r="13" spans="1:26" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
@@ -512,7 +520,7 @@
         <v>6</v>
       </c>
       <c r="C13" s="4">
-        <v>4718730</v>
+        <v>857640</v>
       </c>
     </row>
     <row r="14" spans="1:26" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
@@ -523,7 +531,7 @@
         <v>6</v>
       </c>
       <c r="C14" s="4">
-        <v>2200410</v>
+        <v>2716080</v>
       </c>
     </row>
     <row r="15" spans="1:26" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
@@ -534,7 +542,7 @@
         <v>6</v>
       </c>
       <c r="C15" s="4">
-        <v>73320</v>
+        <v>1381240</v>
       </c>
     </row>
     <row r="16" spans="1:26" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
@@ -545,7 +553,7 @@
         <v>6</v>
       </c>
       <c r="C16" s="4">
-        <v>419420</v>
+        <v>4718730</v>
       </c>
     </row>
     <row r="17" spans="1:3" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
@@ -556,7 +564,7 @@
         <v>6</v>
       </c>
       <c r="C17" s="4">
-        <v>2044780</v>
+        <v>2200410</v>
       </c>
     </row>
     <row r="18" spans="1:3" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
@@ -567,6 +575,39 @@
         <v>6</v>
       </c>
       <c r="C18" s="4">
+        <v>73320</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A19" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="4">
+        <v>419420</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A20" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="4">
+        <v>2044780</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A21" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21" s="4">
         <v>340920</v>
       </c>
     </row>

--- a/uploads/invoice-fee.xlsx
+++ b/uploads/invoice-fee.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Coralis\Eksport Implementasi\20251114\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\coralis\20251202\fix\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7F10C8D-0B2B-4F59-8485-2D3327AB2B26}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12585"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sales Outstanding Fee" sheetId="1" r:id="rId1"/>
@@ -19,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="33">
   <si>
     <t>nomor_invoice</t>
   </si>
@@ -36,25 +37,52 @@
     <t>ex: angka</t>
   </si>
   <si>
-    <t>14BSB25003328</t>
+    <t>02BSB24000550</t>
   </si>
   <si>
     <t>Ongkos Kirim</t>
   </si>
   <si>
-    <t>02BSB24000550</t>
-  </si>
-  <si>
     <t>05ASB25012983</t>
   </si>
   <si>
+    <t>10BSB25000037</t>
+  </si>
+  <si>
+    <t>10BSB25000055</t>
+  </si>
+  <si>
+    <t>10BSB25000064</t>
+  </si>
+  <si>
+    <t>10BSB25000067</t>
+  </si>
+  <si>
+    <t>10BSB25000074</t>
+  </si>
+  <si>
+    <t>10BSB25000075</t>
+  </si>
+  <si>
+    <t>10BSB25000076</t>
+  </si>
+  <si>
+    <t>10BSB25000077</t>
+  </si>
+  <si>
+    <t>10BSB25000078</t>
+  </si>
+  <si>
+    <t>10BSE25000001</t>
+  </si>
+  <si>
+    <t>10BSE25000005</t>
+  </si>
+  <si>
     <t>17BSB25000146</t>
   </si>
   <si>
     <t>17BSB25000171</t>
-  </si>
-  <si>
-    <t>17BSB25000268</t>
   </si>
   <si>
     <t>17BSB24000189</t>
@@ -96,7 +124,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -361,11 +389,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:Z21"/>
+  <dimension ref="A1:Z30"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:26" x14ac:dyDescent="0.2">
@@ -421,7 +449,7 @@
         <v>6</v>
       </c>
       <c r="C4" s="4">
-        <v>7</v>
+        <v>1171171</v>
       </c>
     </row>
     <row r="5" spans="1:26" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
@@ -432,7 +460,7 @@
         <v>6</v>
       </c>
       <c r="C5" s="4">
-        <v>1171171</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:26" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
@@ -443,7 +471,7 @@
         <v>6</v>
       </c>
       <c r="C6" s="4">
-        <v>6</v>
+        <v>270362</v>
       </c>
     </row>
     <row r="7" spans="1:26" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
@@ -454,7 +482,7 @@
         <v>6</v>
       </c>
       <c r="C7" s="4">
-        <v>2343000</v>
+        <v>405406</v>
       </c>
     </row>
     <row r="8" spans="1:26" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
@@ -465,7 +493,7 @@
         <v>6</v>
       </c>
       <c r="C8" s="4">
-        <v>912070</v>
+        <v>45036</v>
       </c>
     </row>
     <row r="9" spans="1:26" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
@@ -476,7 +504,7 @@
         <v>6</v>
       </c>
       <c r="C9" s="4">
-        <v>1009031</v>
+        <v>360360</v>
       </c>
     </row>
     <row r="10" spans="1:26" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
@@ -487,7 +515,7 @@
         <v>6</v>
       </c>
       <c r="C10" s="4">
-        <v>1519940</v>
+        <v>112612</v>
       </c>
     </row>
     <row r="11" spans="1:26" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
@@ -498,7 +526,7 @@
         <v>6</v>
       </c>
       <c r="C11" s="4">
-        <v>3467820</v>
+        <v>135145</v>
       </c>
     </row>
     <row r="12" spans="1:26" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
@@ -509,7 +537,7 @@
         <v>6</v>
       </c>
       <c r="C12" s="4">
-        <v>878130</v>
+        <v>153154</v>
       </c>
     </row>
     <row r="13" spans="1:26" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
@@ -520,7 +548,7 @@
         <v>6</v>
       </c>
       <c r="C13" s="4">
-        <v>857640</v>
+        <v>90090</v>
       </c>
     </row>
     <row r="14" spans="1:26" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
@@ -531,7 +559,7 @@
         <v>6</v>
       </c>
       <c r="C14" s="4">
-        <v>2716080</v>
+        <v>180179</v>
       </c>
     </row>
     <row r="15" spans="1:26" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
@@ -542,7 +570,7 @@
         <v>6</v>
       </c>
       <c r="C15" s="4">
-        <v>1381240</v>
+        <v>112606</v>
       </c>
     </row>
     <row r="16" spans="1:26" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
@@ -553,7 +581,7 @@
         <v>6</v>
       </c>
       <c r="C16" s="4">
-        <v>4718730</v>
+        <v>500000</v>
       </c>
     </row>
     <row r="17" spans="1:3" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
@@ -564,7 +592,7 @@
         <v>6</v>
       </c>
       <c r="C17" s="4">
-        <v>2200410</v>
+        <v>2343000</v>
       </c>
     </row>
     <row r="18" spans="1:3" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
@@ -575,7 +603,7 @@
         <v>6</v>
       </c>
       <c r="C18" s="4">
-        <v>73320</v>
+        <v>912070</v>
       </c>
     </row>
     <row r="19" spans="1:3" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
@@ -586,7 +614,7 @@
         <v>6</v>
       </c>
       <c r="C19" s="4">
-        <v>419420</v>
+        <v>1519940</v>
       </c>
     </row>
     <row r="20" spans="1:3" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
@@ -597,7 +625,7 @@
         <v>6</v>
       </c>
       <c r="C20" s="4">
-        <v>2044780</v>
+        <v>3467820</v>
       </c>
     </row>
     <row r="21" spans="1:3" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
@@ -608,6 +636,105 @@
         <v>6</v>
       </c>
       <c r="C21" s="4">
+        <v>878130</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A22" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" s="4">
+        <v>857640</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A23" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C23" s="4">
+        <v>2716080</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A24" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C24" s="4">
+        <v>1381240</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A25" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C25" s="4">
+        <v>4718730</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A26" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C26" s="4">
+        <v>2200410</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A27" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" s="4">
+        <v>73320</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A28" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="4">
+        <v>419420</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A29" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" s="4">
+        <v>2044780</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A30" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="4">
         <v>340920</v>
       </c>
     </row>

--- a/uploads/invoice-fee.xlsx
+++ b/uploads/invoice-fee.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\coralis\20251202\fix\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Coralis\Eksport Implementasi\20251215\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7F10C8D-0B2B-4F59-8485-2D3327AB2B26}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12585"/>
   </bookViews>
   <sheets>
     <sheet name="Sales Outstanding Fee" sheetId="1" r:id="rId1"/>
@@ -20,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="31">
   <si>
     <t>nomor_invoice</t>
   </si>
@@ -37,16 +36,10 @@
     <t>ex: angka</t>
   </si>
   <si>
-    <t>02BSB24000550</t>
+    <t>10BSB25000037</t>
   </si>
   <si>
     <t>Ongkos Kirim</t>
-  </si>
-  <si>
-    <t>05ASB25012983</t>
-  </si>
-  <si>
-    <t>10BSB25000037</t>
   </si>
   <si>
     <t>10BSB25000055</t>
@@ -124,7 +117,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -389,11 +382,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:Z30"/>
+  <dimension ref="A1:Z28"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:26" x14ac:dyDescent="0.2">
@@ -449,7 +442,7 @@
         <v>6</v>
       </c>
       <c r="C4" s="4">
-        <v>1171171</v>
+        <v>270362</v>
       </c>
     </row>
     <row r="5" spans="1:26" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
@@ -460,7 +453,7 @@
         <v>6</v>
       </c>
       <c r="C5" s="4">
-        <v>6</v>
+        <v>405406</v>
       </c>
     </row>
     <row r="6" spans="1:26" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
@@ -471,7 +464,7 @@
         <v>6</v>
       </c>
       <c r="C6" s="4">
-        <v>270362</v>
+        <v>45036</v>
       </c>
     </row>
     <row r="7" spans="1:26" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
@@ -482,7 +475,7 @@
         <v>6</v>
       </c>
       <c r="C7" s="4">
-        <v>405406</v>
+        <v>360360</v>
       </c>
     </row>
     <row r="8" spans="1:26" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
@@ -493,7 +486,7 @@
         <v>6</v>
       </c>
       <c r="C8" s="4">
-        <v>45036</v>
+        <v>112612</v>
       </c>
     </row>
     <row r="9" spans="1:26" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
@@ -504,7 +497,7 @@
         <v>6</v>
       </c>
       <c r="C9" s="4">
-        <v>360360</v>
+        <v>135145</v>
       </c>
     </row>
     <row r="10" spans="1:26" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
@@ -515,7 +508,7 @@
         <v>6</v>
       </c>
       <c r="C10" s="4">
-        <v>112612</v>
+        <v>153154</v>
       </c>
     </row>
     <row r="11" spans="1:26" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
@@ -526,7 +519,7 @@
         <v>6</v>
       </c>
       <c r="C11" s="4">
-        <v>135145</v>
+        <v>90090</v>
       </c>
     </row>
     <row r="12" spans="1:26" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
@@ -537,7 +530,7 @@
         <v>6</v>
       </c>
       <c r="C12" s="4">
-        <v>153154</v>
+        <v>180179</v>
       </c>
     </row>
     <row r="13" spans="1:26" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
@@ -548,7 +541,7 @@
         <v>6</v>
       </c>
       <c r="C13" s="4">
-        <v>90090</v>
+        <v>112606</v>
       </c>
     </row>
     <row r="14" spans="1:26" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
@@ -559,7 +552,7 @@
         <v>6</v>
       </c>
       <c r="C14" s="4">
-        <v>180179</v>
+        <v>500000</v>
       </c>
     </row>
     <row r="15" spans="1:26" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
@@ -570,7 +563,7 @@
         <v>6</v>
       </c>
       <c r="C15" s="4">
-        <v>112606</v>
+        <v>2343000</v>
       </c>
     </row>
     <row r="16" spans="1:26" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
@@ -581,7 +574,7 @@
         <v>6</v>
       </c>
       <c r="C16" s="4">
-        <v>500000</v>
+        <v>912070</v>
       </c>
     </row>
     <row r="17" spans="1:3" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
@@ -592,7 +585,7 @@
         <v>6</v>
       </c>
       <c r="C17" s="4">
-        <v>2343000</v>
+        <v>1519940</v>
       </c>
     </row>
     <row r="18" spans="1:3" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
@@ -603,7 +596,7 @@
         <v>6</v>
       </c>
       <c r="C18" s="4">
-        <v>912070</v>
+        <v>3467820</v>
       </c>
     </row>
     <row r="19" spans="1:3" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
@@ -614,7 +607,7 @@
         <v>6</v>
       </c>
       <c r="C19" s="4">
-        <v>1519940</v>
+        <v>878130</v>
       </c>
     </row>
     <row r="20" spans="1:3" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
@@ -625,7 +618,7 @@
         <v>6</v>
       </c>
       <c r="C20" s="4">
-        <v>3467820</v>
+        <v>857640</v>
       </c>
     </row>
     <row r="21" spans="1:3" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
@@ -636,7 +629,7 @@
         <v>6</v>
       </c>
       <c r="C21" s="4">
-        <v>878130</v>
+        <v>2716080</v>
       </c>
     </row>
     <row r="22" spans="1:3" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
@@ -647,7 +640,7 @@
         <v>6</v>
       </c>
       <c r="C22" s="4">
-        <v>857640</v>
+        <v>1381240</v>
       </c>
     </row>
     <row r="23" spans="1:3" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
@@ -658,7 +651,7 @@
         <v>6</v>
       </c>
       <c r="C23" s="4">
-        <v>2716080</v>
+        <v>4718730</v>
       </c>
     </row>
     <row r="24" spans="1:3" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
@@ -669,7 +662,7 @@
         <v>6</v>
       </c>
       <c r="C24" s="4">
-        <v>1381240</v>
+        <v>2200410</v>
       </c>
     </row>
     <row r="25" spans="1:3" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
@@ -680,7 +673,7 @@
         <v>6</v>
       </c>
       <c r="C25" s="4">
-        <v>4718730</v>
+        <v>73320</v>
       </c>
     </row>
     <row r="26" spans="1:3" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
@@ -691,7 +684,7 @@
         <v>6</v>
       </c>
       <c r="C26" s="4">
-        <v>2200410</v>
+        <v>419420</v>
       </c>
     </row>
     <row r="27" spans="1:3" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
@@ -702,7 +695,7 @@
         <v>6</v>
       </c>
       <c r="C27" s="4">
-        <v>73320</v>
+        <v>2044780</v>
       </c>
     </row>
     <row r="28" spans="1:3" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
@@ -713,28 +706,6 @@
         <v>6</v>
       </c>
       <c r="C28" s="4">
-        <v>419420</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A29" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C29" s="4">
-        <v>2044780</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A30" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C30" s="4">
         <v>340920</v>
       </c>
     </row>
